--- a/Property Data Collection Template.xlsx
+++ b/Property Data Collection Template.xlsx
@@ -35,7 +35,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. There is one tab per property. Copy a property tab to add more.</t>
+          <t xml:space="preserve">1. There is one tab per property (Property 1, Property 2, …). Copy a property tab to add more.</t>
         </is>
       </c>
     </row>
@@ -49,59 +49,59 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">3. Rates are DECIMALS: 0.05 means 5%. (In Excel you can format the cell as a percentage; the stored value is still the decimal.)</t>
+          <t xml:space="preserve">3. Start by filling "Property name" and "State" at the top, then work down the tiers.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">4. Dates are YYYY-MM-DD text (e.g. 2019-06-01).</t>
+          <t xml:space="preserve">4. Rates are DECIMALS: 0.05 means 5%. (In Excel you can format the cell as a percentage; the stored value is still the decimal.)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5. Years are a 4-digit year, or the word "hold" for no sale / no conversion.</t>
+          <t xml:space="preserve">5. Dates are YYYY-MM-DD text (e.g. 2019-06-01).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">6. TRUE/FALSE fields: type TRUE or FALSE.</t>
+          <t xml:space="preserve">6. Years are a 4-digit year, or the word "hold" for no sale / no conversion.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">7. Peak vs off-season occupancy are separate — fill both if the property is a seasonal short-term rental.</t>
+          <t xml:space="preserve">7. TRUE/FALSE fields: type TRUE or FALSE.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8. Peak vs off-season occupancy are separate — fill both if the property is a seasonal short-term rental.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Importing:</t>
+          <t xml:space="preserve">9. You can leave any field blank — the app fills a sensible default (e.g. 30-year mortgage term, 6% selling costs).</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t xml:space="preserve">- In the app, open the Data tab and choose "Import from Excel (.xlsx)". The file is read on your device only; nothing is uploaded.</t>
-        </is>
-      </c>
+      <c r="A13"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">- After importing, review the numbers, then use "Save scenario (JSON)" to keep them on your device.</t>
+          <t xml:space="preserve">See the EXAMPLE-Format tab for a fully filled-in property you can copy the style from.</t>
         </is>
       </c>
     </row>
@@ -111,15 +111,46 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">The README, EXAMPLE-Format and any Portfolio-Summary tabs are ignored on import — only property tabs are read.</t>
+          <t xml:space="preserve">Importing:</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- In the app, open the Data tab and choose "Import from Excel (.xlsx)". The file is read on your device only; nothing is uploaded.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- Only tabs that contain data are imported. Empty property tabs are skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">- After importing, review the numbers, then use "Save scenario (JSON)" to keep them on your device.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">The README, EXAMPLE-Format and any Portfolio-Summary tabs are ignored on import — only property tabs are read.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t xml:space="preserve">NOTE: Every value already in this template is FICTIONAL DEMO data. Replace it with your own.</t>
         </is>
